--- a/M3 Supply.xlsx
+++ b/M3 Supply.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gladys.ngeno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96D6718A-D850-4322-8D31-C4B3AF977065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F031CC8-2F24-4193-9529-BB1EF3A50F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A713DB86-5155-48EB-B600-AB8D1643B716}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$144</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -129,9 +132,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -470,11 +474,12 @@
   <dimension ref="A1:C1032336"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="9" style="2"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B1" t="s">
@@ -485,7 +490,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>2014</v>
       </c>
       <c r="B2" t="s">
@@ -496,7 +501,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>2014</v>
       </c>
       <c r="B3" t="s">
@@ -507,7 +512,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>2014</v>
       </c>
       <c r="B4" t="s">
@@ -518,7 +523,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>2014</v>
       </c>
       <c r="B5" t="s">
@@ -529,7 +534,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>2014</v>
       </c>
       <c r="B6" t="s">
@@ -540,7 +545,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>2014</v>
       </c>
       <c r="B7" t="s">
@@ -551,7 +556,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>2014</v>
       </c>
       <c r="B8" t="s">
@@ -562,7 +567,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>2014</v>
       </c>
       <c r="B9" t="s">
@@ -573,7 +578,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>2014</v>
       </c>
       <c r="B10" t="s">
@@ -584,7 +589,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>2014</v>
       </c>
       <c r="B11" t="s">
@@ -595,7 +600,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="2">
         <v>2014</v>
       </c>
       <c r="B12" t="s">
@@ -606,7 +611,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="2">
         <v>2014</v>
       </c>
       <c r="B13" t="s">
@@ -617,7 +622,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="A14" s="2">
         <v>2015</v>
       </c>
       <c r="B14" t="s">
@@ -628,7 +633,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="2">
         <v>2015</v>
       </c>
       <c r="B15" t="s">
@@ -639,7 +644,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="2">
         <v>2015</v>
       </c>
       <c r="B16" t="s">
@@ -650,7 +655,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="2">
         <v>2015</v>
       </c>
       <c r="B17" t="s">
@@ -661,7 +666,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="2">
         <v>2015</v>
       </c>
       <c r="B18" t="s">
@@ -672,7 +677,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="2">
         <v>2015</v>
       </c>
       <c r="B19" t="s">
@@ -683,7 +688,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="2">
         <v>2015</v>
       </c>
       <c r="B20" t="s">
@@ -694,7 +699,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="2">
         <v>2015</v>
       </c>
       <c r="B21" t="s">
@@ -705,7 +710,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="2">
         <v>2015</v>
       </c>
       <c r="B22" t="s">
@@ -716,7 +721,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="2">
         <v>2015</v>
       </c>
       <c r="B23" t="s">
@@ -727,7 +732,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" s="2">
         <v>2015</v>
       </c>
       <c r="B24" t="s">
@@ -738,7 +743,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" s="2">
         <v>2015</v>
       </c>
       <c r="B25" t="s">
@@ -749,7 +754,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="A26" s="2">
         <v>2016</v>
       </c>
       <c r="B26" t="s">
@@ -760,7 +765,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="A27" s="2">
         <v>2016</v>
       </c>
       <c r="B27" t="s">
@@ -771,7 +776,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="A28" s="2">
         <v>2016</v>
       </c>
       <c r="B28" t="s">
@@ -782,7 +787,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="A29" s="2">
         <v>2016</v>
       </c>
       <c r="B29" t="s">
@@ -793,7 +798,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="A30" s="2">
         <v>2016</v>
       </c>
       <c r="B30" t="s">
@@ -804,7 +809,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="A31" s="2">
         <v>2016</v>
       </c>
       <c r="B31" t="s">
@@ -815,7 +820,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="A32" s="2">
         <v>2016</v>
       </c>
       <c r="B32" t="s">
@@ -826,7 +831,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="A33" s="2">
         <v>2016</v>
       </c>
       <c r="B33" t="s">
@@ -837,7 +842,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="A34" s="2">
         <v>2016</v>
       </c>
       <c r="B34" t="s">
@@ -848,7 +853,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="A35" s="2">
         <v>2016</v>
       </c>
       <c r="B35" t="s">
@@ -859,7 +864,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="A36" s="2">
         <v>2016</v>
       </c>
       <c r="B36" t="s">
@@ -870,7 +875,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="A37" s="2">
         <v>2016</v>
       </c>
       <c r="B37" t="s">
@@ -881,7 +886,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="A38" s="2">
         <v>2017</v>
       </c>
       <c r="B38" t="s">
@@ -892,7 +897,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="A39" s="2">
         <v>2017</v>
       </c>
       <c r="B39" t="s">
@@ -903,7 +908,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="A40" s="2">
         <v>2017</v>
       </c>
       <c r="B40" t="s">
@@ -914,7 +919,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="A41" s="2">
         <v>2017</v>
       </c>
       <c r="B41" t="s">
@@ -925,7 +930,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="A42" s="2">
         <v>2017</v>
       </c>
       <c r="B42" t="s">
@@ -936,7 +941,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="A43" s="2">
         <v>2017</v>
       </c>
       <c r="B43" t="s">
@@ -947,7 +952,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="A44" s="2">
         <v>2017</v>
       </c>
       <c r="B44" t="s">
@@ -958,7 +963,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="A45" s="2">
         <v>2017</v>
       </c>
       <c r="B45" t="s">
@@ -969,7 +974,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="A46" s="2">
         <v>2017</v>
       </c>
       <c r="B46" t="s">
@@ -980,7 +985,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47">
+      <c r="A47" s="2">
         <v>2017</v>
       </c>
       <c r="B47" t="s">
@@ -991,7 +996,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="A48" s="2">
         <v>2017</v>
       </c>
       <c r="B48" t="s">
@@ -1002,7 +1007,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49">
+      <c r="A49" s="2">
         <v>2017</v>
       </c>
       <c r="B49" t="s">
@@ -1013,7 +1018,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50">
+      <c r="A50" s="2">
         <v>2018</v>
       </c>
       <c r="B50" t="s">
@@ -1024,7 +1029,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51">
+      <c r="A51" s="2">
         <v>2018</v>
       </c>
       <c r="B51" t="s">
@@ -1035,7 +1040,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52">
+      <c r="A52" s="2">
         <v>2018</v>
       </c>
       <c r="B52" t="s">
@@ -1046,7 +1051,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53">
+      <c r="A53" s="2">
         <v>2018</v>
       </c>
       <c r="B53" t="s">
@@ -1057,7 +1062,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54">
+      <c r="A54" s="2">
         <v>2018</v>
       </c>
       <c r="B54" t="s">
@@ -1068,7 +1073,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55">
+      <c r="A55" s="2">
         <v>2018</v>
       </c>
       <c r="B55" t="s">
@@ -1079,7 +1084,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56">
+      <c r="A56" s="2">
         <v>2018</v>
       </c>
       <c r="B56" t="s">
@@ -1090,7 +1095,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57">
+      <c r="A57" s="2">
         <v>2018</v>
       </c>
       <c r="B57" t="s">
@@ -1101,7 +1106,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58">
+      <c r="A58" s="2">
         <v>2018</v>
       </c>
       <c r="B58" t="s">
@@ -1112,7 +1117,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59">
+      <c r="A59" s="2">
         <v>2018</v>
       </c>
       <c r="B59" t="s">
@@ -1123,7 +1128,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60">
+      <c r="A60" s="2">
         <v>2018</v>
       </c>
       <c r="B60" t="s">
@@ -1134,7 +1139,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61">
+      <c r="A61" s="2">
         <v>2018</v>
       </c>
       <c r="B61" t="s">
@@ -1145,7 +1150,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62">
+      <c r="A62" s="2">
         <v>2019</v>
       </c>
       <c r="B62" t="s">
@@ -1156,7 +1161,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63">
+      <c r="A63" s="2">
         <v>2019</v>
       </c>
       <c r="B63" t="s">
@@ -1167,7 +1172,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64">
+      <c r="A64" s="2">
         <v>2019</v>
       </c>
       <c r="B64" t="s">
@@ -1178,7 +1183,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65">
+      <c r="A65" s="2">
         <v>2019</v>
       </c>
       <c r="B65" t="s">
@@ -1189,7 +1194,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66">
+      <c r="A66" s="2">
         <v>2019</v>
       </c>
       <c r="B66" t="s">
@@ -1200,7 +1205,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67">
+      <c r="A67" s="2">
         <v>2019</v>
       </c>
       <c r="B67" t="s">
@@ -1211,7 +1216,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68">
+      <c r="A68" s="2">
         <v>2019</v>
       </c>
       <c r="B68" t="s">
@@ -1222,7 +1227,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69">
+      <c r="A69" s="2">
         <v>2019</v>
       </c>
       <c r="B69" t="s">
@@ -1233,7 +1238,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70">
+      <c r="A70" s="2">
         <v>2019</v>
       </c>
       <c r="B70" t="s">
@@ -1244,7 +1249,7 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71">
+      <c r="A71" s="2">
         <v>2019</v>
       </c>
       <c r="B71" t="s">
@@ -1255,7 +1260,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72">
+      <c r="A72" s="2">
         <v>2019</v>
       </c>
       <c r="B72" t="s">
@@ -1266,7 +1271,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73">
+      <c r="A73" s="2">
         <v>2019</v>
       </c>
       <c r="B73" t="s">
@@ -1277,7 +1282,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74">
+      <c r="A74" s="2">
         <v>2020</v>
       </c>
       <c r="B74" t="s">
@@ -1288,7 +1293,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75">
+      <c r="A75" s="2">
         <v>2020</v>
       </c>
       <c r="B75" t="s">
@@ -1299,7 +1304,7 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76">
+      <c r="A76" s="2">
         <v>2020</v>
       </c>
       <c r="B76" t="s">
@@ -1310,7 +1315,7 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77">
+      <c r="A77" s="2">
         <v>2020</v>
       </c>
       <c r="B77" t="s">
@@ -1321,7 +1326,7 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78">
+      <c r="A78" s="2">
         <v>2020</v>
       </c>
       <c r="B78" t="s">
@@ -1332,7 +1337,7 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79">
+      <c r="A79" s="2">
         <v>2020</v>
       </c>
       <c r="B79" t="s">
@@ -1343,7 +1348,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80">
+      <c r="A80" s="2">
         <v>2020</v>
       </c>
       <c r="B80" t="s">
@@ -1354,7 +1359,7 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81">
+      <c r="A81" s="2">
         <v>2020</v>
       </c>
       <c r="B81" t="s">
@@ -1365,7 +1370,7 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82">
+      <c r="A82" s="2">
         <v>2020</v>
       </c>
       <c r="B82" t="s">
@@ -1376,7 +1381,7 @@
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83">
+      <c r="A83" s="2">
         <v>2020</v>
       </c>
       <c r="B83" t="s">
@@ -1387,7 +1392,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84">
+      <c r="A84" s="2">
         <v>2020</v>
       </c>
       <c r="B84" t="s">
@@ -1398,7 +1403,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85">
+      <c r="A85" s="2">
         <v>2020</v>
       </c>
       <c r="B85" t="s">
@@ -1409,7 +1414,7 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86">
+      <c r="A86" s="2">
         <v>2021</v>
       </c>
       <c r="B86" t="s">
@@ -1420,7 +1425,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87">
+      <c r="A87" s="2">
         <v>2021</v>
       </c>
       <c r="B87" t="s">
@@ -1431,7 +1436,7 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88">
+      <c r="A88" s="2">
         <v>2021</v>
       </c>
       <c r="B88" t="s">
@@ -1442,7 +1447,7 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89">
+      <c r="A89" s="2">
         <v>2021</v>
       </c>
       <c r="B89" t="s">
@@ -1453,7 +1458,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90">
+      <c r="A90" s="2">
         <v>2021</v>
       </c>
       <c r="B90" t="s">
@@ -1464,7 +1469,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91">
+      <c r="A91" s="2">
         <v>2021</v>
       </c>
       <c r="B91" t="s">
@@ -1475,7 +1480,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92">
+      <c r="A92" s="2">
         <v>2021</v>
       </c>
       <c r="B92" t="s">
@@ -1486,7 +1491,7 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93">
+      <c r="A93" s="2">
         <v>2021</v>
       </c>
       <c r="B93" t="s">
@@ -1497,7 +1502,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94">
+      <c r="A94" s="2">
         <v>2021</v>
       </c>
       <c r="B94" t="s">
@@ -1508,7 +1513,7 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95">
+      <c r="A95" s="2">
         <v>2021</v>
       </c>
       <c r="B95" t="s">
@@ -1519,7 +1524,7 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96">
+      <c r="A96" s="2">
         <v>2021</v>
       </c>
       <c r="B96" t="s">
@@ -1530,7 +1535,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97">
+      <c r="A97" s="2">
         <v>2021</v>
       </c>
       <c r="B97" t="s">
@@ -1541,7 +1546,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98">
+      <c r="A98" s="2">
         <v>2022</v>
       </c>
       <c r="B98" t="s">
@@ -1552,7 +1557,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99">
+      <c r="A99" s="2">
         <v>2022</v>
       </c>
       <c r="B99" t="s">
@@ -1563,7 +1568,7 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100">
+      <c r="A100" s="2">
         <v>2022</v>
       </c>
       <c r="B100" t="s">
@@ -1574,7 +1579,7 @@
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101">
+      <c r="A101" s="2">
         <v>2022</v>
       </c>
       <c r="B101" t="s">
@@ -1585,7 +1590,7 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102">
+      <c r="A102" s="2">
         <v>2022</v>
       </c>
       <c r="B102" t="s">
@@ -1596,7 +1601,7 @@
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103">
+      <c r="A103" s="2">
         <v>2022</v>
       </c>
       <c r="B103" t="s">
@@ -1607,7 +1612,7 @@
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104">
+      <c r="A104" s="2">
         <v>2022</v>
       </c>
       <c r="B104" t="s">
@@ -1618,7 +1623,7 @@
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105">
+      <c r="A105" s="2">
         <v>2022</v>
       </c>
       <c r="B105" t="s">
@@ -1629,7 +1634,7 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106">
+      <c r="A106" s="2">
         <v>2022</v>
       </c>
       <c r="B106" t="s">
@@ -1640,7 +1645,7 @@
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107">
+      <c r="A107" s="2">
         <v>2022</v>
       </c>
       <c r="B107" t="s">
@@ -1651,7 +1656,7 @@
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108">
+      <c r="A108" s="2">
         <v>2022</v>
       </c>
       <c r="B108" t="s">
@@ -1662,7 +1667,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109">
+      <c r="A109" s="2">
         <v>2022</v>
       </c>
       <c r="B109" t="s">
@@ -1673,7 +1678,7 @@
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110">
+      <c r="A110" s="2">
         <v>2023</v>
       </c>
       <c r="B110" t="s">
@@ -1684,7 +1689,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111">
+      <c r="A111" s="2">
         <v>2023</v>
       </c>
       <c r="B111" t="s">
@@ -1695,7 +1700,7 @@
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112">
+      <c r="A112" s="2">
         <v>2023</v>
       </c>
       <c r="B112" t="s">
@@ -1706,7 +1711,7 @@
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113">
+      <c r="A113" s="2">
         <v>2023</v>
       </c>
       <c r="B113" t="s">
@@ -1717,7 +1722,7 @@
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114">
+      <c r="A114" s="2">
         <v>2023</v>
       </c>
       <c r="B114" t="s">
@@ -1728,7 +1733,7 @@
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115">
+      <c r="A115" s="2">
         <v>2023</v>
       </c>
       <c r="B115" t="s">
@@ -1739,7 +1744,7 @@
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116">
+      <c r="A116" s="2">
         <v>2023</v>
       </c>
       <c r="B116" t="s">
@@ -1750,7 +1755,7 @@
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117">
+      <c r="A117" s="2">
         <v>2023</v>
       </c>
       <c r="B117" t="s">
@@ -1761,7 +1766,7 @@
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118">
+      <c r="A118" s="2">
         <v>2023</v>
       </c>
       <c r="B118" t="s">
@@ -1772,7 +1777,7 @@
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119">
+      <c r="A119" s="2">
         <v>2023</v>
       </c>
       <c r="B119" t="s">
@@ -1783,7 +1788,7 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120">
+      <c r="A120" s="2">
         <v>2023</v>
       </c>
       <c r="B120" t="s">
@@ -1794,7 +1799,7 @@
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121">
+      <c r="A121" s="2">
         <v>2023</v>
       </c>
       <c r="B121" t="s">
@@ -1805,7 +1810,7 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122">
+      <c r="A122" s="2">
         <v>2024</v>
       </c>
       <c r="B122" t="s">
@@ -1816,7 +1821,7 @@
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123">
+      <c r="A123" s="2">
         <v>2024</v>
       </c>
       <c r="B123" t="s">
@@ -1827,7 +1832,7 @@
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124">
+      <c r="A124" s="2">
         <v>2024</v>
       </c>
       <c r="B124" t="s">
@@ -1838,7 +1843,7 @@
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125">
+      <c r="A125" s="2">
         <v>2024</v>
       </c>
       <c r="B125" t="s">
@@ -1849,7 +1854,7 @@
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126">
+      <c r="A126" s="2">
         <v>2024</v>
       </c>
       <c r="B126" t="s">
@@ -1860,7 +1865,7 @@
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127">
+      <c r="A127" s="2">
         <v>2024</v>
       </c>
       <c r="B127" t="s">
@@ -1871,7 +1876,7 @@
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128">
+      <c r="A128" s="2">
         <v>2024</v>
       </c>
       <c r="B128" t="s">
@@ -1882,7 +1887,7 @@
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129">
+      <c r="A129" s="2">
         <v>2024</v>
       </c>
       <c r="B129" t="s">
@@ -1893,7 +1898,7 @@
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130">
+      <c r="A130" s="2">
         <v>2024</v>
       </c>
       <c r="B130" t="s">
@@ -1904,7 +1909,7 @@
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131">
+      <c r="A131" s="2">
         <v>2024</v>
       </c>
       <c r="B131" t="s">
@@ -1915,7 +1920,7 @@
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132">
+      <c r="A132" s="2">
         <v>2024</v>
       </c>
       <c r="B132" t="s">
@@ -1926,7 +1931,7 @@
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133">
+      <c r="A133" s="2">
         <v>2024</v>
       </c>
       <c r="B133" t="s">
@@ -1937,7 +1942,7 @@
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134">
+      <c r="A134" s="2">
         <v>2025</v>
       </c>
       <c r="B134" t="s">
@@ -1948,7 +1953,7 @@
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135">
+      <c r="A135" s="2">
         <v>2025</v>
       </c>
       <c r="B135" t="s">
@@ -1959,7 +1964,7 @@
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136">
+      <c r="A136" s="2">
         <v>2025</v>
       </c>
       <c r="B136" t="s">
@@ -1970,7 +1975,7 @@
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137">
+      <c r="A137" s="2">
         <v>2025</v>
       </c>
       <c r="B137" t="s">
@@ -1981,7 +1986,7 @@
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138">
+      <c r="A138" s="2">
         <v>2025</v>
       </c>
       <c r="B138" t="s">
@@ -1992,7 +1997,7 @@
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139">
+      <c r="A139" s="2">
         <v>2025</v>
       </c>
       <c r="B139" t="s">
@@ -2003,7 +2008,7 @@
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140">
+      <c r="A140" s="2">
         <v>2025</v>
       </c>
       <c r="B140" t="s">
@@ -2014,7 +2019,7 @@
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141">
+      <c r="A141" s="2">
         <v>2025</v>
       </c>
       <c r="B141" t="s">
@@ -2025,7 +2030,7 @@
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142">
+      <c r="A142" s="2">
         <v>2025</v>
       </c>
       <c r="B142" t="s">
@@ -2036,7 +2041,7 @@
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143">
+      <c r="A143" s="2">
         <v>2025</v>
       </c>
       <c r="B143" t="s">
@@ -2047,7 +2052,7 @@
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144">
+      <c r="A144" s="2">
         <v>2025</v>
       </c>
       <c r="B144" t="s">
